--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\BBQ\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21307AF5-3E02-4FF2-9F48-D1E5882EA898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6869602-7392-4E3F-82AE-2CF9D3492D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="14290" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -211,6 +211,18 @@
   </si>
   <si>
     <t>CardDatas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EncounterDataTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EncounterDatas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EncounterData</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -583,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -819,6 +831,20 @@
         <v>51</v>
       </c>
     </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6869602-7392-4E3F-82AE-2CF9D3492D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72421DC0-698D-440D-96F5-B3A993B927A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -223,6 +223,30 @@
   </si>
   <si>
     <t>EncounterData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelDataTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelDatas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DifficultyDatas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DifficultyData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DifficultyDataTable</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -595,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -845,6 +869,34 @@
         <v>53</v>
       </c>
     </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72421DC0-698D-440D-96F5-B3A993B927A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263D3161-2B21-4444-963B-FA465809A554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>##var</t>
   </si>
@@ -247,6 +247,18 @@
   </si>
   <si>
     <t>DifficultyDataTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TileDataTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TileData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TileDatas</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -619,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -897,6 +909,20 @@
         <v>58</v>
       </c>
     </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263D3161-2B21-4444-963B-FA465809A554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23C12A5-8ABA-44C3-8377-5F034F41E2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -259,6 +259,30 @@
   </si>
   <si>
     <t>TileDatas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InstantEncounterDataTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InstantEncounterData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OptionDataTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OptionData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>InstantEncounterDatas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>OptionDatas</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -631,7 +655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -923,6 +947,34 @@
         <v>63</v>
       </c>
     </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23C12A5-8ABA-44C3-8377-5F034F41E2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4562EAE3-36F7-4BF1-81C8-7AE36F2980F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
   <si>
     <t>##var</t>
   </si>
@@ -283,6 +283,18 @@
   </si>
   <si>
     <t>OptionDatas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityDataTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EntityDatas</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -655,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -808,170 +820,184 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
-        <v>34</v>
+      <c r="B10" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D19" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B21" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D22" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>69</v>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4562EAE3-36F7-4BF1-81C8-7AE36F2980F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796B487B-E264-44D7-B334-15F3CFE07028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
@@ -295,6 +295,18 @@
   </si>
   <si>
     <t>EntityDatas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffDataTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuffDatas</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -667,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -1001,6 +1013,20 @@
         <v>69</v>
       </c>
     </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B25" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796B487B-E264-44D7-B334-15F3CFE07028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112B6088-EAC1-43C0-BE44-BC8847971D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -307,6 +307,18 @@
   </si>
   <si>
     <t>BuffDatas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReputationDataTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReputationData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReputationDatas</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -679,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -1027,6 +1039,20 @@
         <v>75</v>
       </c>
     </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B27" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112B6088-EAC1-43C0-BE44-BC8847971D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E22839-4884-4330-AB1C-6CB0511A58BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E22839-4884-4330-AB1C-6CB0511A58BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF014E2-15F3-4649-86DA-AED837CEF598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="82">
   <si>
     <t>##var</t>
   </si>
@@ -319,6 +319,18 @@
   </si>
   <si>
     <t>ReputationDatas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuideStepDataTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuideStepData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuideStepDatas</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -691,18 +703,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.58203125" customWidth="1"/>
     <col min="4" max="4" width="48.5" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="14.08203125" customWidth="1"/>
     <col min="7" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -737,7 +749,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -769,7 +781,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -792,7 +804,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -809,27 +821,27 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="5" t="s">
         <v>32</v>
       </c>
@@ -843,7 +855,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
         <v>70</v>
       </c>
@@ -857,7 +869,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>34</v>
       </c>
@@ -871,7 +883,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>39</v>
       </c>
@@ -885,7 +897,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>40</v>
       </c>
@@ -899,7 +911,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>43</v>
       </c>
@@ -913,7 +925,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>46</v>
       </c>
@@ -927,7 +939,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>49</v>
       </c>
@@ -941,7 +953,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>52</v>
       </c>
@@ -955,7 +967,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>55</v>
       </c>
@@ -969,7 +981,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>60</v>
       </c>
@@ -983,7 +995,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>61</v>
       </c>
@@ -997,7 +1009,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>64</v>
       </c>
@@ -1011,7 +1023,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>66</v>
       </c>
@@ -1025,7 +1037,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>73</v>
       </c>
@@ -1039,7 +1051,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>76</v>
       </c>
@@ -1051,6 +1063,20 @@
       </c>
       <c r="E27" s="3" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF014E2-15F3-4649-86DA-AED837CEF598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00C0038-9EE0-44B8-BB7A-A6905C0CDB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="85">
   <si>
     <t>##var</t>
   </si>
@@ -331,6 +331,18 @@
   </si>
   <si>
     <t>GuideStepDatas</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridShapeDataTable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridShapeData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GridShapeDatas</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -703,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.33203125" customWidth="1"/>
@@ -1079,6 +1091,20 @@
         <v>81</v>
       </c>
     </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
